--- a/XBRL-template-MFRS/14-Notes-RelatedParty.xlsx
+++ b/XBRL-template-MFRS/14-Notes-RelatedParty.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,15 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -89,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -107,6 +116,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,12 +497,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>

--- a/XBRL-template-MFRS/14-Notes-RelatedParty.xlsx
+++ b/XBRL-template-MFRS/14-Notes-RelatedParty.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +55,48 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,8 +113,20 @@
         <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -94,11 +148,22 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9DEE5"/>
+      </bottom>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -122,6 +187,36 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,338 +583,379 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="9" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Notes - Related party transactions</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="D3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>*Disclosure of transactions between related parties</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="18" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Related party transactions</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Contribution to fund</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Disposal of subsidiaries</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Dividend income</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Interest income</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Issue of shares for exchangeable bonds</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="18" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Key management personnel</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Key management personnel services fee</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Management fees</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Other expenses</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Other key management personnel</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Other revenue</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="18" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Provision of education and staff training services</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="18" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Provision of leasing and hire purchase facilities</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="18" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Purchases of goods</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="18" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Purchases of property and other assets</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="18" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Rental expense</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Rental income</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Revenue from sale of goods</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="18" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Revenue from rendering of services</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="18" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="18" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Royalty income</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="18" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Sales of property and other assets</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Services received</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="18" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Share options recharged</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Share-based payment transactions</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="18" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Supplemental payments and signature bonus</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="18" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Transactions with shareholders and governments</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="18" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Other related parties transactions</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="18" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Outstanding balances for related party transactions</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>*Amounts payable</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="18" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>*Amounts receivable</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="18" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>*Other outstanding balances</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
